--- a/data/procesamiento/matriz_datos_ia.xlsx
+++ b/data/procesamiento/matriz_datos_ia.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-11 20:53:08.326825</t>
+          <t>2026-08-02 14:01:30.791721</t>
         </is>
       </c>
     </row>

--- a/data/procesamiento/matriz_datos_ia.xlsx
+++ b/data/procesamiento/matriz_datos_ia.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-02 14:01:30.791721</t>
+          <t>2026-08-09 01:07:41.037918</t>
         </is>
       </c>
     </row>
